--- a/research/yjs-manual-opt/swiss/products/v23/i18n/workbooks/it.xlsx
+++ b/research/yjs-manual-opt/swiss/products/v23/i18n/workbooks/it.xlsx
@@ -4625,7 +4625,7 @@
         <v>**真空密封后袋子漏气**</v>
       </c>
       <c r="E184" t="str">
-        <v>**真空密封后袋子漏气**</v>
+        <v>**Perdita del sacchetto dopo il sottovuoto**</v>
       </c>
       <c r="F184" t="str">
         <v>review</v>
@@ -4648,7 +4648,7 @@
         <v>高温胶布破损或脱落</v>
       </c>
       <c r="E185" t="str">
-        <v>高温胶布破损或脱落</v>
+        <v>Il nastro ad alta temperatura è danneggiato o staccato</v>
       </c>
       <c r="F185" t="str">
         <v>review</v>
@@ -4671,7 +4671,7 @@
         <v>及时替换高温胶布。</v>
       </c>
       <c r="E186" t="str">
-        <v>及时替换高温胶布。</v>
+        <v>Sostituire tempestivamente il nastro ad alta temperatura.</v>
       </c>
       <c r="F186" t="str">
         <v>review</v>
@@ -4694,7 +4694,7 @@
         <v>发热温度异常导致袋子融化或密封不充分</v>
       </c>
       <c r="E187" t="str">
-        <v>发热温度异常导致袋子融化或密封不充分</v>
+        <v>Una temperatura di saldatura anomala scioglie il sacchetto o causa una saldatura insufficiente</v>
       </c>
       <c r="F187" t="str">
         <v>review</v>
@@ -4717,7 +4717,7 @@
         <v>参考抽气不干净和不能密封的解决方案。</v>
       </c>
       <c r="E188" t="str">
-        <v>参考抽气不干净和不能密封的解决方案。</v>
+        <v>Fare riferimento alle soluzioni per vuoto insufficiente o mancata saldatura.</v>
       </c>
       <c r="F188" t="str">
         <v>review</v>
@@ -4740,7 +4740,7 @@
         <v>锋利物品刺穿袋子</v>
       </c>
       <c r="E189" t="str">
-        <v>锋利物品刺穿袋子</v>
+        <v>Oggetti appuntiti perforano il sacchetto</v>
       </c>
       <c r="F189" t="str">
         <v>review</v>
@@ -4763,7 +4763,7 @@
         <v>用纸巾或防刺穿片包裹锋利边缘，使用新袋重试。</v>
       </c>
       <c r="E190" t="str">
-        <v>用纸巾或防刺穿片包裹锋利边缘，使用新袋重试。</v>
+        <v>Avvolgere i bordi appuntiti con carta assorbente o una protezione anti-perforazione e riprovare con un nuovo sacchetto.</v>
       </c>
       <c r="F190" t="str">
         <v>review</v>
@@ -5177,7 +5177,7 @@
         <v>一些水果和蔬菜在包装前如果没有正确地焯熟，或者热的食物，会释放气体，导致真空袋没有收紧，此类情况属于正常表现，不属于漏气。</v>
       </c>
       <c r="E208" t="str">
-        <v>一些水果和蔬菜在包装前如果没有正确地焯熟，或者热的食物，会释放气体，导致真空袋没有收紧，此类情况属于正常表现，不属于漏气。</v>
+        <v>Alcuni frutti e ortaggi possono rilasciare gas se non vengono sbollentati correttamente prima del confezionamento. Anche i cibi caldi possono rilasciare gas. Se in questi casi il sacchetto non rimane ben teso, è normale e non indica una perdita.</v>
       </c>
       <c r="F208" t="str">
         <v>review</v>
@@ -5200,7 +5200,7 @@
         <v>提示</v>
       </c>
       <c r="E209" t="str">
-        <v>提示</v>
+        <v>Nota</v>
       </c>
       <c r="F209" t="str">
         <v>review</v>
@@ -5223,7 +5223,7 @@
         <v>若以上故障排除方案均无法解决问题，请联系客服指引解决，请不要擅自拆卸机器。</v>
       </c>
       <c r="E210" t="str">
-        <v>若以上故障排除方案均无法解决问题，请联系客服指引解决，请不要擅自拆卸机器。</v>
+        <v>Se il problema non si risolve con le soluzioni sopra indicate, contattare il servizio clienti. Non smontare la macchina da soli.</v>
       </c>
       <c r="F210" t="str">
         <v>review</v>
@@ -5499,7 +5499,7 @@
         <v>**错误报警（蜂鸣声长鸣 + 指示灯快闪）**</v>
       </c>
       <c r="E222" t="str">
-        <v>**错误报警（蜂鸣声长鸣 + 指示灯快闪）**</v>
+        <v>**Allarme di errore (bip continuo + spia lampeggiante veloce)**</v>
       </c>
       <c r="F222" t="str">
         <v>review</v>
@@ -5522,7 +5522,7 @@
         <v>按下 Vac&amp;Seal/Start 或 Seal 后报警</v>
       </c>
       <c r="E223" t="str">
-        <v>按下 Vac&amp;Seal/Start 或 Seal 后报警</v>
+        <v>Allarme dopo aver premuto Vac&amp;Seal/Start o Seal</v>
       </c>
       <c r="F223" t="str">
         <v>review</v>
@@ -5545,7 +5545,7 @@
         <v>检查面盖是否闭合，把手是否已下压锁紧。</v>
       </c>
       <c r="E224" t="str">
-        <v>检查面盖是否闭合，把手是否已下压锁紧。</v>
+        <v>Verificare che il coperchio sia chiuso e che la maniglia sia abbassata e bloccata.</v>
       </c>
       <c r="F224" t="str">
         <v>review</v>
@@ -5568,7 +5568,7 @@
         <v>真空工作过程中连续蜂鸣</v>
       </c>
       <c r="E225" t="str">
-        <v>真空工作过程中连续蜂鸣</v>
+        <v>Bip continuo durante il vuoto</v>
       </c>
       <c r="F225" t="str">
         <v>review</v>
@@ -5591,7 +5591,7 @@
         <v>机器无法达到目标压力，检查把手锁紧及袋子是否破损，更换新袋重试。</v>
       </c>
       <c r="E226" t="str">
-        <v>机器无法达到目标压力，检查把手锁紧及袋子是否破损，更换新袋重试。</v>
+        <v>La macchina non raggiunge la pressione target. Verificare che la maniglia sia bloccata e che il sacchetto non sia danneggiato. Riprovare con un nuovo sacchetto.</v>
       </c>
       <c r="F226" t="str">
         <v>review</v>
@@ -5637,7 +5637,7 @@
         <v>如因特殊原因，导致液体进入机器内部的处理方案</v>
       </c>
       <c r="E228" t="str">
-        <v>如因特殊原因，导致液体进入机器内部的处理方案</v>
+        <v>Procedura da seguire se, per cause particolari, del liquido entra all'interno della macchina</v>
       </c>
       <c r="F228" t="str">
         <v>review</v>
@@ -5660,7 +5660,7 @@
         <v>**液体进入真空腔中：**</v>
       </c>
       <c r="E229" t="str">
-        <v>**液体进入真空腔中：**</v>
+        <v>**Liquido nella camera del vuoto:**</v>
       </c>
       <c r="F229" t="str">
         <v>review</v>
@@ -5683,7 +5683,7 @@
         <v>立即关闭电源，等待至少 5 分钟，让机器发热器冷却。</v>
       </c>
       <c r="E230" t="str">
-        <v>立即关闭电源，等待至少 5 分钟，让机器发热器冷却。</v>
+        <v>Spegnere immediatamente la macchina e attendere almeno 5 minuti affinché il riscaldatore si raffreddi.</v>
       </c>
       <c r="F230" t="str">
         <v>review</v>
@@ -5706,7 +5706,7 @@
         <v>将液体槽取出，并清理擦干液体。</v>
       </c>
       <c r="E231" t="str">
-        <v>将液体槽取出，并清理擦干液体。</v>
+        <v>Rimuovere la vaschetta dei liquidi e asciugare il liquido.</v>
       </c>
       <c r="F231" t="str">
         <v>review</v>
@@ -5729,7 +5729,7 @@
         <v>将真空腔中的液体擦干。</v>
       </c>
       <c r="E232" t="str">
-        <v>将真空腔中的液体擦干。</v>
+        <v>Asciugare il liquido all'interno della camera del vuoto.</v>
       </c>
       <c r="F232" t="str">
         <v>review</v>
@@ -5752,7 +5752,7 @@
         <v>将机器底部铺垫厨房纸或托盘，重新通电。</v>
       </c>
       <c r="E233" t="str">
-        <v>将机器底部铺垫厨房纸或托盘，重新通电。</v>
+        <v>Posizionare carta da cucina o un vassoio sotto la macchina, quindi riaccenderla.</v>
       </c>
       <c r="F233" t="str">
         <v>review</v>
@@ -5775,7 +5775,7 @@
         <v>合上面盖，长按 [btn:Pulse Vac] 按键抽气 20 秒，然后点击 [btn:Stop] 排气，重复 5 次，让内部管道的液体排出。</v>
       </c>
       <c r="E234" t="str">
-        <v>合上面盖，长按 [btn:Pulse Vac] 按键抽气 20 秒，然后点击 [btn:Stop] 排气，重复 5 次，让内部管道的液体排出。</v>
+        <v>Chiudere il coperchio, tenere premuto [btn:Pulse Vac] per 20 secondi, quindi premere [btn:Stop] per sfiatare. Ripetere 5 volte per espellere il liquido dai condotti interni.</v>
       </c>
       <c r="F234" t="str">
         <v>review</v>
@@ -5798,7 +5798,7 @@
         <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 48 小时，期间不要翻倒机器。</v>
       </c>
       <c r="E235" t="str">
-        <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 48 小时，期间不要翻倒机器。</v>
+        <v>Aprire il coperchio, posizionare carta da cucina o un vassoio sotto la macchina e lasciarla asciugare in un luogo ventilato per 48 ore. Non inclinare né capovolgere la macchina.</v>
       </c>
       <c r="F235" t="str">
         <v>review</v>
@@ -5821,7 +5821,7 @@
         <v>**液体进入发热器：**</v>
       </c>
       <c r="E236" t="str">
-        <v>**液体进入发热器：**</v>
+        <v>**Liquido nel riscaldatore:**</v>
       </c>
       <c r="F236" t="str">
         <v>review</v>
@@ -5844,7 +5844,7 @@
         <v>请勿翻倒机器，关闭电源，等待 10 分钟，让发热器冷却及内部液体排出。</v>
       </c>
       <c r="E237" t="str">
-        <v>请勿翻倒机器，关闭电源，等待 10 分钟，让发热器冷却及内部液体排出。</v>
+        <v>Non capovolgere la macchina. Spegnerla e attendere 10 minuti affinché il riscaldatore si raffreddi e il liquido interno defluisca.</v>
       </c>
       <c r="F237" t="str">
         <v>review</v>
@@ -5867,7 +5867,7 @@
         <v>清理和擦干机器接水盘、真空腔、底部的液体。</v>
       </c>
       <c r="E238" t="str">
-        <v>清理和擦干机器接水盘、真空腔、底部的液体。</v>
+        <v>Pulire e asciugare la vaschetta raccogligocce, la camera del vuoto e il liquido sul fondo della macchina.</v>
       </c>
       <c r="F238" t="str">
         <v>review</v>
@@ -5890,7 +5890,7 @@
         <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 24 小时，期间不要翻倒机器。</v>
       </c>
       <c r="E239" t="str">
-        <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 24 小时，期间不要翻倒机器。</v>
+        <v>Aprire il coperchio, posizionare carta da cucina o un vassoio sotto la macchina e lasciarla asciugare in un luogo ventilato per 24 ore. Non inclinare né capovolgere la macchina.</v>
       </c>
       <c r="F239" t="str">
         <v>review</v>
@@ -5913,7 +5913,7 @@
         <v>将机器底部铺垫厨房纸或托盘，重新通电。</v>
       </c>
       <c r="E240" t="str">
-        <v>将机器底部铺垫厨房纸或托盘，重新通电。</v>
+        <v>Posizionare carta da cucina o un vassoio sotto la macchina, quindi riaccenderla.</v>
       </c>
       <c r="F240" t="str">
         <v>review</v>
@@ -5936,7 +5936,7 @@
         <v>合上面盖，长按 [btn:Pulse Vac] 按键抽气 20 秒，然后点击 [btn:Stop] 排气，重复 5 次，让内部管道的液体排出。</v>
       </c>
       <c r="E241" t="str">
-        <v>合上面盖，长按 [btn:Pulse Vac] 按键抽气 20 秒，然后点击 [btn:Stop] 排气，重复 5 次，让内部管道的液体排出。</v>
+        <v>Chiudere il coperchio, tenere premuto [btn:Pulse Vac] per 20 secondi, quindi premere [btn:Stop] per sfiatare. Ripetere 5 volte per espellere il liquido dai condotti interni.</v>
       </c>
       <c r="F241" t="str">
         <v>review</v>
@@ -5959,7 +5959,7 @@
         <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 48 小时，期间不要翻倒机器。</v>
       </c>
       <c r="E242" t="str">
-        <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 48 小时，期间不要翻倒机器。</v>
+        <v>Aprire il coperchio, posizionare carta da cucina o un vassoio sotto la macchina e lasciarla asciugare in un luogo ventilato per 48 ore. Non inclinare né capovolgere la macchina.</v>
       </c>
       <c r="F242" t="str">
         <v>review</v>
@@ -5982,7 +5982,7 @@
         <v>如果长期不清洁，内部管道可能会堵塞，影响抽气性能，此时请联系售后进行管道更换。</v>
       </c>
       <c r="E243" t="str">
-        <v>如果长期不清洁，内部管道可能会堵塞，影响抽气性能，此时请联系售后进行管道更换。</v>
+        <v>Se i condotti interni non vengono puliti per lungo tempo, potrebbero ostruirsi e ridurre le prestazioni di aspirazione. Contattare l'assistenza post-vendita per la sostituzione dei condotti.</v>
       </c>
       <c r="F243" t="str">
         <v>review</v>
@@ -6005,7 +6005,7 @@
         <v>注意</v>
       </c>
       <c r="E244" t="str">
-        <v>注意</v>
+        <v>Attenzione</v>
       </c>
       <c r="F244" t="str">
         <v>review</v>
